--- a/Scripts_inesdattatreya/data_output/GS2_25-24_sessions/risk_ratio_satis_plot/Session_240924/NA_check_class_and_satisfaction_Session_240924.xlsx
+++ b/Scripts_inesdattatreya/data_output/GS2_25-24_sessions/risk_ratio_satis_plot/Session_240924/NA_check_class_and_satisfaction_Session_240924.xlsx
@@ -388,22 +388,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>177</v>
+      </c>
+      <c r="F2">
         <v>112</v>
-      </c>
-      <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>189</v>
       </c>
     </row>
   </sheetData>
